--- a/examples/data/RetailWorkbook.xlsx
+++ b/examples/data/RetailWorkbook.xlsx
@@ -60,7 +60,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
